--- a/backend/src/main/resources/templates/archiveExportTemplate.xlsx
+++ b/backend/src/main/resources/templates/archiveExportTemplate.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethan/Mac本地文稿/0-本地项目/GezhiPlatform/src/main/resources/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethan/Mac本地文稿/0-本地项目/GezhiPlatform/backend/src/main/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E13A45E-5B2F-A145-856F-00056189EDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B1FE3B-2ABE-084B-A1AA-9C87FCA1D166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5480" yWindow="2360" windowWidth="29400" windowHeight="16740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学生信息登记表" sheetId="1" r:id="rId1"/>
+    <sheet name="健康声明表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
   <si>
     <t>性别</t>
   </si>
@@ -140,22 +141,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>健康申明</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>身体状态</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>心理状态</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>健康状况</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>关注问题</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -168,10 +153,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>导出人：{exporter}   导出时间：{exportTime}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>{stuNo}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -288,39 +269,63 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{physicalHealthStatus}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{physicalHealthIssue}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{physicalMedicationUse}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{physicalTreatment}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{mentalHealthStatus}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{mentalHealthIssue}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{mentalMedicationUse}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{mentalTreatment}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>{rin}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出时间</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{exporter}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{exportTime}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据创建时间</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPart.category}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPart.healthIssue}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPart.medicationUse}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPart.ongoingTreatment}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPart.createdAt}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>健康声明</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>请见下页</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{healthPartTips}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -328,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -398,6 +403,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -417,7 +429,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -477,13 +489,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC4C4C4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC4C4C4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC4C4C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -514,6 +539,81 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -530,37 +630,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -571,29 +647,20 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -601,6 +668,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC4C4C4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -850,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.3984375" customWidth="1"/>
@@ -864,65 +936,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="40.5" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1">
-      <c r="A2" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="A2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="30"/>
       <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="E2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="30"/>
       <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="20"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -930,425 +1008,325 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="34"/>
+      <c r="F6" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
+      <c r="B8" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
+      <c r="F8" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="B9" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="B11" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
+      <c r="F12" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="B13" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" ht="16">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="18" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="25"/>
+      <c r="B16" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="25"/>
+      <c r="F16" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
+      <c r="B17" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="F17" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="44"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" spans="1:8" ht="35" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
+      <c r="B18" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
+      <c r="F18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="1:8" ht="16">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="18" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="35" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25"/>
+      <c r="B21" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25"/>
+      <c r="F21" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="22"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22"/>
+      <c r="A22" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" ht="16">
-      <c r="A24" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
-    </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-    </row>
-    <row r="27" spans="1:8" ht="60" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="36"/>
-    </row>
-    <row r="28" spans="1:8" ht="60" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="23" t="s">
+      <c r="A23" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="36"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" ht="18" customHeight="1">
+      <c r="A24" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B12:D12"/>
+  <mergeCells count="31">
     <mergeCell ref="F12:H12"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:H15"/>
@@ -1360,6 +1338,155 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A3848A-E2BC-594A-8E1C-DB1E45F03A4F}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="10.3984375" customWidth="1"/>
+    <col min="2" max="4" width="23.59765625" customWidth="1"/>
+    <col min="5" max="5" width="14.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="47"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1">
+      <c r="A2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" ht="18" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5" ht="18" customHeight="1">
+      <c r="A6" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+    </row>
+    <row r="7" spans="1:5" ht="16">
+      <c r="A7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="70" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
